--- a/data/trans_orig/P70A_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P70A_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si dichos problemas de salud fueron causados por su trabajo en 2023</t>
+          <t>Población según si su ausencia en el trabajo por motivos de salud, fue debido a problemas de salud causados por su trabajo en 2023 (tasa de respuesta: 94,01%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9585</t>
+          <t>9086</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20358</t>
+          <t>20265</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11540</t>
+          <t>11553</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16253</t>
+          <t>16154</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22082</t>
+          <t>22677</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35099</t>
+          <t>34873</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>55,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>85,54%</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11622</t>
+          <t>10189</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>631</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5245</t>
+          <t>5232</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1763</t>
+          <t>1810</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12633</t>
+          <t>12262</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>30,08%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2186</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12327</t>
+          <t>12310</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1229</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>1746</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13346</t>
+          <t>12441</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>30,52%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>346184</t>
+          <t>345711</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>479733</t>
+          <t>476314</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>154629</t>
+          <t>155277</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>176246</t>
+          <t>176883</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>515800</t>
+          <t>512430</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>669803</t>
+          <t>677508</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>70,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>93,42%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8694</t>
+          <t>11772</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>77032</t>
+          <t>76971</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,49 +1314,49 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
+          <t>15,38%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>26019</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>18662</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>34635</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>11,57%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>8,3%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
           <t>15,4%</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>26019</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>18733</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>35129</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>11,57%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>8,33%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>15,62%</t>
-        </is>
-      </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>76</t>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>22754</t>
+          <t>21561</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>101723</t>
+          <t>99684</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,74%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9682</t>
+          <t>10244</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>82908</t>
+          <t>83351</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24882</t>
+          <t>24718</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42694</t>
+          <t>42833</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30749</t>
+          <t>27762</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>116506</t>
+          <t>117383</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,19%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>88931</t>
+          <t>88236</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>105043</t>
+          <t>104558</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>97479</t>
+          <t>97781</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>115199</t>
+          <t>114865</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>193695</t>
+          <t>190699</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>215794</t>
+          <t>215521</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>77,2%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,25%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3184</t>
+          <t>3373</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14106</t>
+          <t>15283</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6176</t>
+          <t>6297</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17045</t>
+          <t>17524</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11779</t>
+          <t>11536</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26771</t>
+          <t>26930</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,9%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3749</t>
+          <t>4279</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16355</t>
+          <t>16611</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8968</t>
+          <t>8995</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24963</t>
+          <t>24308</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15649</t>
+          <t>15929</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>34430</t>
+          <t>35777</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,48%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>466632</t>
+          <t>467555</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>606059</t>
+          <t>602534</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>272393</t>
+          <t>273960</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>301791</t>
+          <t>303241</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>761145</t>
+          <t>759893</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>917135</t>
+          <t>927986</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>91,6%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16767</t>
+          <t>16845</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>83324</t>
+          <t>82460</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>29702</t>
+          <t>29792</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>49014</t>
+          <t>49856</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>41366</t>
+          <t>34942</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>119387</t>
+          <t>116921</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,54%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14829</t>
+          <t>16730</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>94187</t>
+          <t>93105</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>37310</t>
+          <t>36932</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>60135</t>
+          <t>60138</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>49986</t>
+          <t>49094</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>139658</t>
+          <t>141771</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,99%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P70A_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P70A_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>15107</t>
+          <t>15065</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9086</t>
+          <t>8914</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20265</t>
+          <t>19364</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>64,53%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>14874</t>
+          <t>16269</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11553</t>
+          <t>12975</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16154</t>
+          <t>18343</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>29982</t>
+          <t>31335</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22677</t>
+          <t>23244</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34873</t>
+          <t>36122</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>73,55%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>55,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,47%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>2599</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10189</t>
+          <t>7316</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1911</t>
+          <t>2646</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>572</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5232</t>
+          <t>5940</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1810</t>
+          <t>2216</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12262</t>
+          <t>11525</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>27,27%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5541</t>
+          <t>5682</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>1916</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12310</t>
+          <t>12744</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>5541</t>
+          <t>5682</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1746</t>
+          <t>2224</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12441</t>
+          <t>13935</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>32,97%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23981</t>
+          <t>23346</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23981</t>
+          <t>23346</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23981</t>
+          <t>23346</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16785</t>
+          <t>18915</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16785</t>
+          <t>18915</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16785</t>
+          <t>18915</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>40766</t>
+          <t>42262</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>40766</t>
+          <t>42262</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40766</t>
+          <t>42262</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>426554</t>
+          <t>200990</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>345711</t>
+          <t>182601</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>476314</t>
+          <t>216169</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>72,0%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>165719</t>
+          <t>179885</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>155277</t>
+          <t>167070</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>176883</t>
+          <t>191237</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>68,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>592273</t>
+          <t>380875</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>512430</t>
+          <t>358926</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>677508</t>
+          <t>399232</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>76,48%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35180</t>
+          <t>36691</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11772</t>
+          <t>25741</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>76971</t>
+          <t>49378</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26019</t>
+          <t>27743</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18662</t>
+          <t>19623</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34635</t>
+          <t>37278</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>61199</t>
+          <t>64433</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>21561</t>
+          <t>50841</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>99684</t>
+          <t>79072</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>15,15%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>38601</t>
+          <t>41462</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10244</t>
+          <t>29653</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>83351</t>
+          <t>56944</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>33170</t>
+          <t>35259</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24718</t>
+          <t>26324</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42833</t>
+          <t>45742</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>71771</t>
+          <t>76721</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27762</t>
+          <t>62237</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>117383</t>
+          <t>94502</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>18,1%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>500335</t>
+          <t>279143</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>500335</t>
+          <t>279143</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>500335</t>
+          <t>279143</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>224908</t>
+          <t>242886</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>224908</t>
+          <t>242886</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>224908</t>
+          <t>242886</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>725243</t>
+          <t>522029</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>725243</t>
+          <t>522029</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>725243</t>
+          <t>522029</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>97868</t>
+          <t>105499</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>88236</t>
+          <t>95316</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>104558</t>
+          <t>112650</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>77,27%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>107492</t>
+          <t>120700</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>97781</t>
+          <t>111409</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>114865</t>
+          <t>127916</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>205360</t>
+          <t>226198</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>190699</t>
+          <t>213089</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>215521</t>
+          <t>236354</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,46%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7483</t>
+          <t>8873</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3373</t>
+          <t>3771</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15283</t>
+          <t>17147</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10942</t>
+          <t>11668</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6297</t>
+          <t>6941</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17524</t>
+          <t>17937</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>18426</t>
+          <t>20542</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11536</t>
+          <t>13516</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26930</t>
+          <t>30932</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,45%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>8862</t>
+          <t>8980</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4279</t>
+          <t>4038</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16611</t>
+          <t>17486</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>14382</t>
+          <t>14528</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8995</t>
+          <t>9121</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24308</t>
+          <t>23824</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>23243</t>
+          <t>23507</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15929</t>
+          <t>15819</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>35777</t>
+          <t>35856</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>13,27%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>114213</t>
+          <t>123352</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>114213</t>
+          <t>123352</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>114213</t>
+          <t>123352</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>132816</t>
+          <t>146896</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>132816</t>
+          <t>146896</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>132816</t>
+          <t>146896</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>247029</t>
+          <t>270247</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>247029</t>
+          <t>270247</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>247029</t>
+          <t>270247</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>539529</t>
+          <t>321554</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>467555</t>
+          <t>302575</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>602534</t>
+          <t>339997</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>288086</t>
+          <t>316853</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>273960</t>
+          <t>299811</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>303241</t>
+          <t>331283</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>827615</t>
+          <t>638408</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>759893</t>
+          <t>615730</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>927986</t>
+          <t>661947</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>79,32%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>45996</t>
+          <t>48163</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16845</t>
+          <t>34965</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>82460</t>
+          <t>63737</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>38872</t>
+          <t>42057</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>29792</t>
+          <t>32257</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>49856</t>
+          <t>53043</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>84868</t>
+          <t>90221</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34942</t>
+          <t>73754</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>116921</t>
+          <t>107328</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>12,86%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>53004</t>
+          <t>56123</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16730</t>
+          <t>41392</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>93105</t>
+          <t>71549</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>47551</t>
+          <t>49786</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>36932</t>
+          <t>38311</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>60138</t>
+          <t>63400</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>100556</t>
+          <t>105910</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>49094</t>
+          <t>87743</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>141771</t>
+          <t>125674</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>15,06%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>638529</t>
+          <t>425841</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>638529</t>
+          <t>425841</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>638529</t>
+          <t>425841</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>374509</t>
+          <t>408697</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>374509</t>
+          <t>408697</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>374509</t>
+          <t>408697</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1013038</t>
+          <t>834538</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1013038</t>
+          <t>834538</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1013038</t>
+          <t>834538</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
